--- a/data/trans_dic/P55$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,47 +717,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,42</t>
+          <t>0,0; 13,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,89</t>
+          <t>0,0; 14,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 12,48</t>
+          <t>1,9; 12,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,98</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,42</t>
+          <t>1,6; 16,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,59</t>
+          <t>0,38; 4,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,31</t>
+          <t>1,08; 10,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 12,28</t>
+          <t>2,07; 12,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,86</t>
+          <t>1,3; 5,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,77</t>
+          <t>0,0; 12,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,76</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,56</t>
+          <t>1,44; 14,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 19,29</t>
+          <t>3,37; 18,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,69; 20,97</t>
+          <t>4,64; 19,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,41</t>
+          <t>1,51; 7,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 13,73</t>
+          <t>3,18; 13,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,76</t>
+          <t>0,76; 7,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 13,14</t>
+          <t>3,06; 13,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 7,5</t>
+          <t>2,2; 7,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,98</t>
+          <t>0,0; 36,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,14</t>
+          <t>0,0; 40,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 22,5</t>
+          <t>2,42; 21,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 18,44</t>
+          <t>2,32; 19,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,55</t>
+          <t>0,0; 9,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,88</t>
+          <t>0,0; 12,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,2</t>
+          <t>1,98; 9,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 19,62</t>
+          <t>3,13; 18,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 14,91</t>
+          <t>1,26; 16,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,1</t>
+          <t>2,88; 10,9</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,47</t>
+          <t>0,0; 14,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,19</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,33</t>
+          <t>0,0; 18,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,38</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 11,21</t>
+          <t>1,29; 12,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,87</t>
+          <t>0,0; 9,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 19,32</t>
+          <t>4,05; 20,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,92</t>
+          <t>4,06; 11,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,83</t>
+          <t>0,99; 9,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,14</t>
+          <t>0,79; 7,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 15,56</t>
+          <t>3,15; 16,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 9,4</t>
+          <t>3,77; 9,25</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 10,48</t>
+          <t>2,15; 10,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 10,18</t>
+          <t>1,4; 11,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 8,75</t>
+          <t>3,01; 8,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,35</t>
+          <t>3,71; 10,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,47</t>
+          <t>0,8; 4,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,54</t>
+          <t>5,28; 12,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,43</t>
+          <t>3,12; 6,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 9,5</t>
+          <t>3,77; 8,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,28</t>
+          <t>1,51; 5,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 9,55</t>
+          <t>3,82; 9,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,46</t>
+          <t>3,31; 6,26</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que no le ayuda nadie cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,47 +1645,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3869</t>
+          <t>0; 4542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3581</t>
+          <t>0; 4011</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>978; 6192</t>
+          <t>945; 6143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5601</t>
+          <t>0; 5552</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 7310</t>
+          <t>0; 5840</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1087; 9273</t>
+          <t>965; 9624</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>302; 3654</t>
+          <t>300; 3315</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>875; 7324</t>
+          <t>850; 7904</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1829; 10797</t>
+          <t>1820; 11180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1643; 7580</t>
+          <t>1687; 7564</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 7094</t>
+          <t>0; 6101</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6282</t>
+          <t>0; 6112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1664</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>553; 5632</t>
+          <t>556; 5513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2960; 13055</t>
+          <t>2279; 12799</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6689</t>
+          <t>0; 7642</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3600; 16112</t>
+          <t>3567; 15188</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1372; 6376</t>
+          <t>1296; 6081</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3927; 15891</t>
+          <t>3674; 15986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1017; 10403</t>
+          <t>1014; 10666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3552; 15476</t>
+          <t>3603; 15793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2760; 9347</t>
+          <t>2740; 9822</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7764</t>
+          <t>0; 7927</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 10935</t>
+          <t>0; 11225</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1704</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>630; 5744</t>
+          <t>617; 5543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1015; 8569</t>
+          <t>1079; 9140</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 4988</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6643</t>
+          <t>0; 6580</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1145; 6529</t>
+          <t>1155; 5768</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2635; 13350</t>
+          <t>2128; 12373</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>966; 11908</t>
+          <t>1003; 12839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7249</t>
+          <t>0; 7466</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2363; 9309</t>
+          <t>2411; 9136</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3576</t>
+          <t>0; 3439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4479</t>
+          <t>0; 5048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5408</t>
+          <t>0; 5340</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4487</t>
+          <t>0; 4365</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>921; 8073</t>
+          <t>930; 8756</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6947</t>
+          <t>0; 7372</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3152; 15228</t>
+          <t>3190; 15768</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4465; 11381</t>
+          <t>4230; 12065</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>936; 9346</t>
+          <t>938; 9367</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>949; 8452</t>
+          <t>931; 8987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3236; 16853</t>
+          <t>3408; 18327</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5060; 13867</t>
+          <t>5559; 13648</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2765; 13269</t>
+          <t>2724; 13387</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2039; 14879</t>
+          <t>2040; 16193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6503</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4824; 13738</t>
+          <t>4722; 14007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8948; 23910</t>
+          <t>8557; 23850</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2341; 12494</t>
+          <t>2238; 13353</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13564; 33523</t>
+          <t>14120; 33383</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10260; 21099</t>
+          <t>10249; 19982</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13766; 33965</t>
+          <t>13473; 31810</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7058; 22497</t>
+          <t>6426; 22914</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15700; 37119</t>
+          <t>14844; 35393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17267; 31358</t>
+          <t>16054; 30365</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$nadie-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$nadie-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,41</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,44</t>
+          <t>0,0; 14,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 12,38</t>
+          <t>1,39; 11,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,4</t>
+          <t>0,0; 12,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,57</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 16,0</t>
+          <t>1,88; 16,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,16</t>
+          <t>0,35; 4,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,05</t>
+          <t>1,11; 9,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,72</t>
+          <t>2,04; 12,12</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,85</t>
+          <t>1,34; 5,7</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,7</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>0,0; 14,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,25</t>
+          <t>1,4; 15,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 18,91</t>
+          <t>4,11; 20,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,65</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 19,76</t>
+          <t>4,83; 20,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,07</t>
+          <t>1,53; 7,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 13,82</t>
+          <t>3,54; 13,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,96</t>
+          <t>0,76; 7,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 13,41</t>
+          <t>3,27; 13,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,88</t>
+          <t>2,17; 7,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,74</t>
+          <t>0,0; 38,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,18</t>
+          <t>0,0; 36,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,71</t>
+          <t>2,28; 21,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 19,67</t>
+          <t>2,08; 18,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,61</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,76</t>
+          <t>0,0; 14,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 9,89</t>
+          <t>1,9; 10,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 18,18</t>
+          <t>3,75; 20,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 16,08</t>
+          <t>1,29; 16,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,98</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 10,9</t>
+          <t>2,97; 11,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,88</t>
+          <t>0,0; 18,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 13,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,1</t>
+          <t>0,0; 20,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,16</t>
+          <t>1,28; 11,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,42</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 20,01</t>
+          <t>4,02; 19,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 11,57</t>
+          <t>4,16; 11,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,85</t>
+          <t>1,0; 9,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,6</t>
+          <t>0,81; 7,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 16,92</t>
+          <t>3,14; 15,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,25</t>
+          <t>3,81; 9,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 10,58</t>
+          <t>2,12; 11,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 11,08</t>
+          <t>1,36; 10,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,92</t>
+          <t>3,06; 8,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,33</t>
+          <t>3,67; 10,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,78</t>
+          <t>0,82; 4,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,49</t>
+          <t>5,32; 12,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,09</t>
+          <t>3,04; 6,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,9</t>
+          <t>3,95; 9,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,38</t>
+          <t>1,52; 5,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 9,1</t>
+          <t>4,0; 9,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,26</t>
+          <t>3,61; 6,53</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4016</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4542</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,52 +1655,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 4023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>945; 6143</t>
+          <t>734; 5926</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5552</t>
+          <t>0; 5683</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5840</t>
+          <t>0; 5905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>965; 9624</t>
+          <t>1129; 9663</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>300; 3315</t>
+          <t>295; 4028</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>850; 7904</t>
+          <t>877; 7189</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5802</t>
+          <t>0; 5891</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1820; 11180</t>
+          <t>1798; 10654</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1687; 7564</t>
+          <t>1845; 7862</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>6009</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6101</t>
+          <t>0; 6008</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6112</t>
+          <t>0; 6584</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1868,47 +1868,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>556; 5513</t>
+          <t>587; 6631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2279; 12799</t>
+          <t>2781; 13898</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 7642</t>
+          <t>0; 6655</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3567; 15188</t>
+          <t>3713; 15765</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1296; 6081</t>
+          <t>1448; 7137</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3674; 15986</t>
+          <t>4101; 16110</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1014; 10666</t>
+          <t>1016; 9774</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3603; 15793</t>
+          <t>3846; 16408</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2740; 9822</t>
+          <t>2961; 10421</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5752</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7927</t>
+          <t>0; 8205</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 11225</t>
+          <t>0; 10192</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,47 +2076,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>617; 5543</t>
+          <t>677; 6287</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1079; 9140</t>
+          <t>964; 8411</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4988</t>
+          <t>0; 5044</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6580</t>
+          <t>0; 7488</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1155; 5768</t>
+          <t>1230; 6704</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2128; 12373</t>
+          <t>2550; 14122</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1003; 12839</t>
+          <t>1029; 13287</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 7466</t>
+          <t>0; 7578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2411; 9136</t>
+          <t>2806; 10807</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>8360</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9639</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3439</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5340</t>
+          <t>0; 6150</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4365</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>930; 8756</t>
+          <t>924; 7934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7372</t>
+          <t>0; 6591</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3190; 15768</t>
+          <t>3170; 15180</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4230; 12065</t>
+          <t>4694; 13454</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>938; 9367</t>
+          <t>953; 9405</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931; 8987</t>
+          <t>955; 9175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3408; 18327</t>
+          <t>3396; 17155</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5559; 13648</t>
+          <t>6004; 15381</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8399</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23124</t>
+          <t>25416</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2724; 13387</t>
+          <t>2680; 14318</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2040; 16193</t>
+          <t>1985; 15764</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 5968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4722; 14007</t>
+          <t>5172; 14989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8557; 23850</t>
+          <t>8471; 23526</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2238; 13353</t>
+          <t>2280; 13169</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14120; 33383</t>
+          <t>14223; 33820</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10249; 19982</t>
+          <t>10871; 23262</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13473; 31810</t>
+          <t>14130; 32718</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6426; 22914</t>
+          <t>6480; 23012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14844; 35393</t>
+          <t>15546; 36057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16054; 30365</t>
+          <t>19009; 34345</t>
         </is>
       </c>
     </row>
